--- a/data/trans_orig/P34B02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34B02-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza gimnasia suave juegos que requieren poco esfuerzo y similares</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza gimnasia suave como juegos que requieren poco esfuerzo y similares (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,3</t>
+          <t>0,16; 0,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,56</t>
+          <t>0,32; 0,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,26</t>
+          <t>0,17; 0,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,41</t>
+          <t>0,29; 0,41</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,4</t>
+          <t>0,3; 0,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,49</t>
+          <t>0,38; 0,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,08</t>
+          <t>0,64; 1,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,73</t>
+          <t>0,45; 0,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,41</t>
+          <t>0,34; 0,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,89</t>
+          <t>0,62; 0,89</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,58</t>
+          <t>0,31; 0,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,86</t>
+          <t>0,51; 0,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,23</t>
+          <t>0,91; 1,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,53</t>
+          <t>0,24; 0,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,55</t>
+          <t>0,34; 0,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,2</t>
+          <t>0,96; 1,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,51</t>
+          <t>0,32; 0,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,65</t>
+          <t>0,47; 0,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,16</t>
+          <t>0,96; 1,18</t>
         </is>
       </c>
     </row>
@@ -1012,27 +1012,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,48</t>
+          <t>0,38; 0,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,98</t>
+          <t>0,69; 0,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,26</t>
+          <t>0,18; 0,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,34</t>
+          <t>0,27; 0,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,71</t>
+          <t>0,52; 0,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,4</t>
+          <t>0,33; 0,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,82</t>
+          <t>0,66; 0,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34B02-Estudios-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,35</t>
         </is>
       </c>
     </row>
@@ -687,22 +687,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,57</t>
+          <t>0,36; 0,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,15</t>
+          <t>0,08; 0,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,27</t>
+          <t>0,14; 0,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,35</t>
+          <t>0,22; 0,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,27</t>
+          <t>0,16; 0,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,41</t>
+          <t>0,3; 0,42</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,9</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,4</t>
+          <t>0,29; 0,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,49</t>
+          <t>0,37; 0,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,1</t>
+          <t>0,95; 1,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,74</t>
+          <t>0,68; 0,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,42</t>
+          <t>0,34; 0,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,89</t>
+          <t>0,84; 0,96</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,03</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,57</t>
+          <t>0,33; 0,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,83</t>
+          <t>0,54; 0,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,23</t>
+          <t>0,88; 1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,52</t>
+          <t>0,25; 0,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,55</t>
+          <t>0,35; 0,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,21</t>
+          <t>0,93; 1,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,5</t>
+          <t>0,31; 0,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,66</t>
+          <t>0,46; 0,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,18</t>
+          <t>0,94; 1,13</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,99</t>
+          <t>0,88; 1,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,25</t>
+          <t>0,19; 0,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,7</t>
+          <t>0,65; 0,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,82</t>
+          <t>0,78; 0,87</t>
         </is>
       </c>
     </row>
